--- a/04_DESIGN_TABLES/DesignTable_4503.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_4503.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O34"/>
+  <dimension ref="A1:Q34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -494,6 +494,16 @@
           <t>$PRP@OMiSKU</t>
         </is>
       </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>DH@BORE</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>$PRP@DimSource</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1998,24 +2008,52 @@
           <t>4503-04-04-FG</t>
         </is>
       </c>
+      <c r="B28" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0.281</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>1/4</t>
+        </is>
+      </c>
       <c r="I28" t="inlineStr">
         <is>
           <t>4503-04-04-FG</t>
         </is>
       </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>1/4-18 (A NPTF)</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 4503-04-04 (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 4503-04-04 (differs by -FG suffix) -&gt; dims NOT copied -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"); sources per cell in CHANGES.csv</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 4503-04-04 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 4503-04-04 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | 2026-10-18 Brennan = yes (staged, not shipped): filled from Brennan ($PRP@DimSource BRENNAN; to undo clear the BRENNAN cells and regenerate); Brennan hose drill 0.189 (DH@BORE) vs threaded-end drill 0.281 (D1@BORE)</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -2026,6 +2064,14 @@
       <c r="O28" t="inlineStr">
         <is>
           <t>4503-04-04-FG</t>
+        </is>
+      </c>
+      <c r="P28" t="n">
+        <v>0.189</v>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
@@ -2035,24 +2081,52 @@
           <t>4503-08-08-FG</t>
         </is>
       </c>
+      <c r="B29" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="C29" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0.531</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>1/2</t>
+        </is>
+      </c>
       <c r="I29" t="inlineStr">
         <is>
           <t>4503-08-08-FG</t>
         </is>
       </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>1/2-14 (A NPTF)</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 4503-08-08 (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 4503-08-08 (differs by -FG suffix) -&gt; dims NOT copied -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"); sources per cell in CHANGES.csv</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 4503-08-08 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 4503-08-08 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | 2026-10-18 Brennan = yes (staged, not shipped): filled from Brennan ($PRP@DimSource BRENNAN; to undo clear the BRENNAN cells and regenerate); Brennan hose drill 0.406 (DH@BORE) vs threaded-end drill 0.531 (D1@BORE)</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -2063,6 +2137,14 @@
       <c r="O29" t="inlineStr">
         <is>
           <t>4503-08-08-FG</t>
+        </is>
+      </c>
+      <c r="P29" t="n">
+        <v>0.406</v>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
@@ -2072,24 +2154,52 @@
           <t>4503-12-12-FG</t>
         </is>
       </c>
+      <c r="B30" t="n">
+        <v>1.894</v>
+      </c>
+      <c r="C30" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="E30" t="n">
+        <v>1.062</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.709</v>
+      </c>
+      <c r="G30" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>3/4</t>
+        </is>
+      </c>
       <c r="I30" t="inlineStr">
         <is>
           <t>4503-12-12-FG</t>
         </is>
       </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>3/4-14 (A NPTF)</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 4503-12-12 (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 4503-12-12 (differs by -FG suffix) -&gt; dims NOT copied -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"); sources per cell in CHANGES.csv</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 4503-12-12 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 4503-12-12 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | 2026-10-18 Brennan = yes (staged, not shipped): filled from Brennan ($PRP@DimSource BRENNAN; to undo clear the BRENNAN cells and regenerate); Brennan hose drill 0.626 (DH@BORE) vs threaded-end drill 0.709 (D1@BORE)</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -2100,6 +2210,14 @@
       <c r="O30" t="inlineStr">
         <is>
           <t>4503-12-12-FG</t>
+        </is>
+      </c>
+      <c r="P30" t="n">
+        <v>0.626</v>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
@@ -2109,24 +2227,52 @@
           <t>4503-16-12-FG</t>
         </is>
       </c>
+      <c r="B31" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="C31" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="D31" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="E31" t="n">
+        <v>1.312</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.719</v>
+      </c>
+      <c r="G31" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="I31" t="inlineStr">
         <is>
           <t>4503-16-12-FG</t>
         </is>
       </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>3/4-14 (A NPTF)</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 4503-16-12 (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 4503-16-12 (differs by -FG suffix) -&gt; dims NOT copied -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"); sources per cell in CHANGES.csv</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 4503-16-12 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 4503-16-12 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | 2026-10-18 Brennan = yes (staged, not shipped): filled from Brennan ($PRP@DimSource BRENNAN; to undo clear the BRENNAN cells and regenerate); Brennan hose drill 0.844 (DH@BORE) vs threaded-end drill 0.719 (D1@BORE)</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -2137,6 +2283,14 @@
       <c r="O31" t="inlineStr">
         <is>
           <t>4503-16-12-FG</t>
+        </is>
+      </c>
+      <c r="P31" t="n">
+        <v>0.844</v>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
@@ -2146,24 +2300,52 @@
           <t>4503-16-16-FG</t>
         </is>
       </c>
+      <c r="B32" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="C32" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="D32" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="E32" t="n">
+        <v>1.312</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.9379999999999999</v>
+      </c>
+      <c r="G32" t="n">
+        <v>1.315</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="I32" t="inlineStr">
         <is>
           <t>4503-16-16-FG</t>
         </is>
       </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>1-11 1/2 (A NPTF)</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 4503-16-16 (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 4503-16-16 (differs by -FG suffix) -&gt; dims NOT copied -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"); sources per cell in CHANGES.csv</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 4503-16-16 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 4503-16-16 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | 2026-10-18 Brennan = yes (staged, not shipped): filled from Brennan ($PRP@DimSource BRENNAN; to undo clear the BRENNAN cells and regenerate); Brennan hose drill 0.843 (DH@BORE) vs threaded-end drill 0.938 (D1@BORE)</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -2174,6 +2356,14 @@
       <c r="O32" t="inlineStr">
         <is>
           <t>4503-16-16-FG</t>
+        </is>
+      </c>
+      <c r="P32" t="n">
+        <v>0.843</v>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
@@ -2183,24 +2373,52 @@
           <t>4503-20-20-FG</t>
         </is>
       </c>
+      <c r="B33" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="C33" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="D33" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="E33" t="n">
+        <v>1.625</v>
+      </c>
+      <c r="F33" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="G33" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>1 1/4</t>
+        </is>
+      </c>
       <c r="I33" t="inlineStr">
         <is>
           <t>4503-20-20-FG</t>
         </is>
       </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>1 1/4-11 1/2 (A NPTF)</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 4503-20-20 (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 4503-20-20 (differs by -FG suffix) -&gt; dims NOT copied -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"); sources per cell in CHANGES.csv</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 4503-20-20 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 4503-20-20 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | 2026-10-18 Brennan = yes (staged, not shipped): filled from Brennan ($PRP@DimSource BRENNAN; to undo clear the BRENNAN cells and regenerate); Brennan hose drill 1.094 (DH@BORE) vs threaded-end drill 1.25 (D1@BORE)</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -2211,6 +2429,14 @@
       <c r="O33" t="inlineStr">
         <is>
           <t>4503-20-20-FG</t>
+        </is>
+      </c>
+      <c r="P33" t="n">
+        <v>1.094</v>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
@@ -2220,24 +2446,52 @@
           <t>4503-24-24-FG</t>
         </is>
       </c>
+      <c r="B34" t="n">
+        <v>2.146</v>
+      </c>
+      <c r="C34" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="D34" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="E34" t="n">
+        <v>1.875</v>
+      </c>
+      <c r="F34" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G34" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>1 1/2</t>
+        </is>
+      </c>
       <c r="I34" t="inlineStr">
         <is>
           <t>4503-24-24-FG</t>
         </is>
       </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>1 1/2-11 1/2 (A NPTF)</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 4503-24-24 (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 4503-24-24 (differs by -FG suffix) -&gt; dims NOT copied -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"); sources per cell in CHANGES.csv</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 4503-24-24 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 4503-24-24 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | 2026-10-18 Brennan = yes (staged, not shipped): filled from Brennan ($PRP@DimSource BRENNAN; to undo clear the BRENNAN cells and regenerate); Brennan hose drill 1.343 (DH@BORE) vs threaded-end drill 1.5 (D1@BORE)</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -2248,6 +2502,14 @@
       <c r="O34" t="inlineStr">
         <is>
           <t>4503-24-24-FG</t>
+        </is>
+      </c>
+      <c r="P34" t="n">
+        <v>1.343</v>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
